--- a/tests/SafeOpenXml.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcf1a468811b74504"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raced5ae9790d4c3e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00db3eedbe574d1e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb40da18ecfc941f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raced5ae9790d4c3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reebc9c8a760c420c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb40da18ecfc941f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9685dba80744a12"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reebc9c8a760c420c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R93941f0d43a84c80"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9685dba80744a12"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80554081ec104fe1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R93941f0d43a84c80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd5914eb50ecf42f9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80554081ec104fe1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raaafd6a9601645a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd5914eb50ecf42f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf456a05dfce84a0f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raaafd6a9601645a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dc06ccd397646d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf456a05dfce84a0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Racf1c021e2f44334"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dc06ccd397646d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R663f7785813a40e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Racf1c021e2f44334"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb6c316759815496a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R663f7785813a40e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e12a73f88c94a3a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb6c316759815496a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1b3fb6f2c60c4867"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e12a73f88c94a3a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R500f9aa9d4914212"/>
   </x:tableParts>
 </x:worksheet>
 </file>